--- a/source_data/Figure8.xlsx
+++ b/source_data/Figure8.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
-    <sheet name="Fig8A1_Chik_Classfic" sheetId="2" r:id="rId2"/>
+    <sheet name="Fig8A1_Chik_Classifi" sheetId="2" r:id="rId2"/>
     <sheet name="Fig8A2_Chik_Criteria" sheetId="3" r:id="rId3"/>
     <sheet name="Fig8A3_Chik_Evolutio" sheetId="4" r:id="rId4"/>
     <sheet name="Fig8B1_Zika_Classifi" sheetId="5" r:id="rId5"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="63">
   <si>
     <t>Sheet</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Rows</t>
   </si>
   <si>
-    <t>Figure 8 — Chikungunya and Zika clinical profile (GraphPad source, through 2025)</t>
+    <t>Figure 8 — Chikungunya and Zika clinical profile (clinical tables 2016-2026, discarded notifications excluded; 2026 = January-September)</t>
   </si>
   <si>
     <t>Generated by pipelines/build_source_data.R</t>
@@ -44,10 +44,10 @@
     <t>Incidence = cases per 100,000 inhabitants</t>
   </si>
   <si>
-    <t>Fig8A1_Chik_Classfic</t>
+    <t>Fig8A1_Chik_Classifi</t>
   </si>
   <si>
-    <t>Chikungunya Classfication 2017-2025: counts and plotted percentages. Percent = share of records with a known value; Excluded_missing rows (ignored/blank) are not plotted</t>
+    <t>Chikungunya Classification 2016-2026: counts and plotted percentages. Percent = share of records with a known value; Excluded_missing rows (ignored/blank) are not plotted</t>
   </si>
   <si>
     <t>plot_proportion (graphpad_pipeline.R)</t>
@@ -56,37 +56,37 @@
     <t>Fig8A2_Chik_Criteria</t>
   </si>
   <si>
-    <t>Chikungunya Criteria 2010 2017-2025: counts and plotted percentages. Percent = share of records with a known value; Excluded_missing rows (ignored/blank) are not plotted</t>
+    <t>Chikungunya Criteria 2016-2026: counts and plotted percentages. Percent = share of records with a known value; Excluded_missing rows (ignored/blank) are not plotted</t>
   </si>
   <si>
     <t>Fig8A3_Chik_Evolutio</t>
   </si>
   <si>
-    <t>Chikungunya Evolution 2013-2025: counts and plotted percentages. Percent = share of records with a known value; Excluded_missing rows (ignored/blank) are not plotted</t>
+    <t>Chikungunya Evolution 2016-2026: counts and plotted percentages. Percent = share of records with a known value; Excluded_missing rows (ignored/blank) are not plotted</t>
   </si>
   <si>
     <t>Fig8B1_Zika_Classifi</t>
   </si>
   <si>
-    <t>Zika Classification 2016-2025: counts and plotted percentages. Percent = share of records with a known value; Excluded_missing rows (ignored/blank) are not plotted</t>
+    <t>Zika Classification 2016-2026: counts and plotted percentages. Percent = share of records with a known value; Excluded_missing rows (ignored/blank) are not plotted</t>
   </si>
   <si>
     <t>Fig8B2_Zika_Criteria</t>
   </si>
   <si>
-    <t>Zika Criteria 2016-2025: counts and plotted percentages. Percent = share of records with a known value; Excluded_missing rows (ignored/blank) are not plotted</t>
+    <t>Zika Criteria 2016-2026: counts and plotted percentages. Percent = share of records with a known value; Excluded_missing rows (ignored/blank) are not plotted</t>
   </si>
   <si>
     <t>Fig8B3_Zika_Evolutio</t>
   </si>
   <si>
-    <t>Zika Evolution 2016-2025: counts and plotted percentages. Percent = share of records with a known value; Excluded_missing rows (ignored/blank) are not plotted</t>
+    <t>Zika Evolution 2016-2026: counts and plotted percentages. Percent = share of records with a known value; Excluded_missing rows (ignored/blank) are not plotted</t>
   </si>
   <si>
     <t>Fig8B4_Zika_Pregnanc</t>
   </si>
   <si>
-    <t>Zika Pregnancy 2016-2025: counts and plotted percentages. Percent = share of records with a known value; Excluded_missing rows (ignored/blank) are not plotted</t>
+    <t>Zika Pregnancy 2016-2026: counts and plotted percentages. Percent = share of records with a known value; Excluded_missing rows (ignored/blank) are not plotted</t>
   </si>
   <si>
     <t>Virus</t>
@@ -113,13 +113,16 @@
     <t>Chikungunya</t>
   </si>
   <si>
-    <t>Classfication 2017-2025</t>
+    <t>Classification 2016-2026</t>
+  </si>
+  <si>
+    <t>2016</t>
+  </si>
+  <si>
+    <t>Ign/Blank</t>
   </si>
   <si>
     <t>2017</t>
-  </si>
-  <si>
-    <t>Ign/Blank</t>
   </si>
   <si>
     <t>2018</t>
@@ -146,10 +149,16 @@
     <t>2025</t>
   </si>
   <si>
-    <t>Descarded</t>
+    <t>2026</t>
   </si>
   <si>
-    <t>Criteria 2010 2017-2025</t>
+    <t>Inconclusive</t>
+  </si>
+  <si>
+    <t>Unclassified</t>
+  </si>
+  <si>
+    <t>Criteria 2016-2026</t>
   </si>
   <si>
     <t>Laboratorial</t>
@@ -161,7 +170,7 @@
     <t>In investigation</t>
   </si>
   <si>
-    <t>Evolution 2013-2025</t>
+    <t>Evolution 2016-2026</t>
   </si>
   <si>
     <t>Cure</t>
@@ -179,34 +188,10 @@
     <t>Zika</t>
   </si>
   <si>
-    <t>Classification 2016-2025</t>
-  </si>
-  <si>
-    <t>2016</t>
-  </si>
-  <si>
     <t>Confirmed</t>
   </si>
   <si>
-    <t>Discarded</t>
-  </si>
-  <si>
-    <t>Inconclusive</t>
-  </si>
-  <si>
-    <t>Criteria 2016-2025</t>
-  </si>
-  <si>
-    <t>Clinical-epidemiological</t>
-  </si>
-  <si>
-    <t>Evolution 2016-2025</t>
-  </si>
-  <si>
-    <t>Other causes</t>
-  </si>
-  <si>
-    <t>Pregnancy 2016-2025</t>
+    <t>Pregnancy 2016-2026</t>
   </si>
   <si>
     <t>1º Trimester</t>
@@ -610,7 +595,7 @@
         <v>9</v>
       </c>
       <c r="D6">
-        <v>27</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -624,7 +609,7 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -638,7 +623,7 @@
         <v>9</v>
       </c>
       <c r="D8">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -652,7 +637,7 @@
         <v>9</v>
       </c>
       <c r="D9">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -666,7 +651,7 @@
         <v>9</v>
       </c>
       <c r="D10">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -680,7 +665,7 @@
         <v>9</v>
       </c>
       <c r="D11">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -694,7 +679,7 @@
         <v>9</v>
       </c>
       <c r="D12">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -704,7 +689,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1">
@@ -744,7 +729,7 @@
         <v>32</v>
       </c>
       <c r="E2">
-        <v>21636</v>
+        <v>1</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -764,7 +749,7 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>13529</v>
+        <v>0</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -784,7 +769,7 @@
         <v>32</v>
       </c>
       <c r="E4">
-        <v>28300</v>
+        <v>0</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -804,7 +789,7 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>29930</v>
+        <v>1</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -824,7 +809,7 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>18139</v>
+        <v>0</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -844,7 +829,7 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>26148</v>
+        <v>0</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -864,7 +849,7 @@
         <v>32</v>
       </c>
       <c r="E8">
-        <v>28171</v>
+        <v>74</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -884,7 +869,7 @@
         <v>32</v>
       </c>
       <c r="E9">
-        <v>32040</v>
+        <v>385</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -904,7 +889,7 @@
         <v>32</v>
       </c>
       <c r="E10">
-        <v>17096</v>
+        <v>0</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -918,19 +903,16 @@
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E11">
-        <v>59647</v>
+        <v>48</v>
       </c>
       <c r="F11" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>26.39177720945461</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -941,19 +923,16 @@
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E12">
-        <v>30678</v>
+        <v>45</v>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>29.15162111824851</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -964,19 +943,19 @@
         <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E13">
-        <v>46438</v>
+        <v>160273</v>
       </c>
       <c r="F13" t="b">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>30.91785509793739</v>
+        <v>67.03122516750174</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -987,19 +966,19 @@
         <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E14">
-        <v>28382</v>
+        <v>166367</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>39.33967233110637</v>
+        <v>88.48555442090034</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1010,19 +989,19 @@
         <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E15">
-        <v>41659</v>
+        <v>74562</v>
       </c>
       <c r="F15" t="b">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>37.58209439953811</v>
+        <v>84.64105707669255</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1033,19 +1012,19 @@
         <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D16" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E16">
-        <v>99520</v>
+        <v>103579</v>
       </c>
       <c r="F16" t="b">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>40.1097860300904</v>
+        <v>78.58920469202872</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1056,19 +1035,19 @@
         <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E17">
-        <v>108076</v>
+        <v>43973</v>
       </c>
       <c r="F17" t="b">
         <v>0</v>
       </c>
       <c r="G17">
-        <v>45.35748459769343</v>
+        <v>59.42457904267683</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1079,19 +1058,19 @@
         <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D18" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E18">
-        <v>161875</v>
+        <v>69195</v>
       </c>
       <c r="F18" t="b">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>41.13796179347536</v>
+        <v>79.2321256813081</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1102,19 +1081,19 @@
         <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E19">
-        <v>124446</v>
+        <v>148607</v>
       </c>
       <c r="F19" t="b">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>53.01620571545422</v>
+        <v>85.07531043010815</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1125,19 +1104,19 @@
         <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D20" t="s">
         <v>29</v>
       </c>
       <c r="E20">
-        <v>166359</v>
+        <v>130196</v>
       </c>
       <c r="F20" t="b">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>73.60822279054538</v>
+        <v>82.39575224823274</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1148,19 +1127,19 @@
         <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D21" t="s">
         <v>29</v>
       </c>
       <c r="E21">
-        <v>74558</v>
+        <v>232047</v>
       </c>
       <c r="F21" t="b">
         <v>0</v>
       </c>
       <c r="G21">
-        <v>70.8483788817515</v>
+        <v>87.88394094789386</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1171,19 +1150,19 @@
         <v>30</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D22" t="s">
         <v>29</v>
       </c>
       <c r="E22">
-        <v>103760</v>
+        <v>110477</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
       </c>
       <c r="G22">
-        <v>69.08214490206261</v>
+        <v>87.22947311904367</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1194,19 +1173,19 @@
         <v>30</v>
       </c>
       <c r="C23" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D23" t="s">
         <v>29</v>
       </c>
       <c r="E23">
-        <v>43764</v>
+        <v>56651</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
       </c>
       <c r="G23">
-        <v>60.66032766889363</v>
+        <v>83.91124672285338</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1217,19 +1196,19 @@
         <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D24" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="E24">
-        <v>69189</v>
+        <v>37473</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>62.4179056004619</v>
+        <v>15.6723908624771</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1240,19 +1219,19 @@
         <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D25" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="E25">
-        <v>148599</v>
+        <v>16</v>
       </c>
       <c r="F25" t="b">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>59.8902139699096</v>
+        <v>0.008509914049868096</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1263,19 +1242,19 @@
         <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D26" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="E26">
-        <v>130200</v>
+        <v>0</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
       </c>
       <c r="G26">
-        <v>54.64251540230657</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1286,19 +1265,19 @@
         <v>30</v>
       </c>
       <c r="C27" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D27" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="E27">
-        <v>231618</v>
+        <v>1</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
       </c>
       <c r="G27">
-        <v>58.86203820652464</v>
+        <v>0.0007587368548839891</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1309,19 +1288,410 @@
         <v>30</v>
       </c>
       <c r="C28" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28" t="s">
+        <v>43</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28" t="b">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29" t="b">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0.001145055649704576</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0.0005724852155693079</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" t="s">
+        <v>43</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31" t="b">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" t="s">
         <v>40</v>
       </c>
-      <c r="D28" t="s">
-        <v>29</v>
-      </c>
-      <c r="E28">
-        <v>110286</v>
-      </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
-      <c r="G28">
-        <v>46.98379428454578</v>
+      <c r="D32" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32" t="b">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" t="s">
+        <v>43</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0.000789571341718581</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" t="s">
+        <v>42</v>
+      </c>
+      <c r="D34" t="s">
+        <v>43</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34" t="b">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" t="s">
+        <v>31</v>
+      </c>
+      <c r="D35" t="s">
+        <v>44</v>
+      </c>
+      <c r="E35">
+        <v>41356</v>
+      </c>
+      <c r="F35" t="b">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>17.29638397002116</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" t="s">
+        <v>29</v>
+      </c>
+      <c r="B36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" t="s">
+        <v>33</v>
+      </c>
+      <c r="D36" t="s">
+        <v>44</v>
+      </c>
+      <c r="E36">
+        <v>21633</v>
+      </c>
+      <c r="F36" t="b">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>11.50593566504978</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" t="s">
+        <v>29</v>
+      </c>
+      <c r="B37" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" t="s">
+        <v>34</v>
+      </c>
+      <c r="D37" t="s">
+        <v>44</v>
+      </c>
+      <c r="E37">
+        <v>13530</v>
+      </c>
+      <c r="F37" t="b">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>15.35894292330745</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" t="s">
+        <v>29</v>
+      </c>
+      <c r="B38" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38" t="s">
+        <v>35</v>
+      </c>
+      <c r="D38" t="s">
+        <v>44</v>
+      </c>
+      <c r="E38">
+        <v>28218</v>
+      </c>
+      <c r="F38" t="b">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>21.41003657111641</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" t="s">
+        <v>29</v>
+      </c>
+      <c r="B39" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" t="s">
+        <v>36</v>
+      </c>
+      <c r="D39" t="s">
+        <v>44</v>
+      </c>
+      <c r="E39">
+        <v>30025</v>
+      </c>
+      <c r="F39" t="b">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>40.57542095732317</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" t="s">
+        <v>29</v>
+      </c>
+      <c r="B40" t="s">
+        <v>30</v>
+      </c>
+      <c r="C40" t="s">
+        <v>37</v>
+      </c>
+      <c r="D40" t="s">
+        <v>44</v>
+      </c>
+      <c r="E40">
+        <v>18136</v>
+      </c>
+      <c r="F40" t="b">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>20.76672926304218</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" t="s">
+        <v>29</v>
+      </c>
+      <c r="B41" t="s">
+        <v>30</v>
+      </c>
+      <c r="C41" t="s">
+        <v>38</v>
+      </c>
+      <c r="D41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E41">
+        <v>26069</v>
+      </c>
+      <c r="F41" t="b">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>14.92411708467629</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" t="s">
+        <v>29</v>
+      </c>
+      <c r="B42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C42" t="s">
+        <v>39</v>
+      </c>
+      <c r="D42" t="s">
+        <v>44</v>
+      </c>
+      <c r="E42">
+        <v>27817</v>
+      </c>
+      <c r="F42" t="b">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>17.60424775176726</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" t="s">
+        <v>29</v>
+      </c>
+      <c r="B43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C43" t="s">
+        <v>40</v>
+      </c>
+      <c r="D43" t="s">
+        <v>44</v>
+      </c>
+      <c r="E43">
+        <v>31991</v>
+      </c>
+      <c r="F43" t="b">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>12.11605905210614</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" t="s">
+        <v>29</v>
+      </c>
+      <c r="B44" t="s">
+        <v>30</v>
+      </c>
+      <c r="C44" t="s">
+        <v>41</v>
+      </c>
+      <c r="D44" t="s">
+        <v>44</v>
+      </c>
+      <c r="E44">
+        <v>16173</v>
+      </c>
+      <c r="F44" t="b">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>12.76973730961461</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" t="s">
+        <v>29</v>
+      </c>
+      <c r="B45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D45" t="s">
+        <v>44</v>
+      </c>
+      <c r="E45">
+        <v>10862</v>
+      </c>
+      <c r="F45" t="b">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>16.08875327714662</v>
       </c>
     </row>
   </sheetData>
@@ -1331,7 +1701,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1">
@@ -1362,7 +1732,7 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C2" t="s">
         <v>31</v>
@@ -1371,7 +1741,7 @@
         <v>32</v>
       </c>
       <c r="E2">
-        <v>20472</v>
+        <v>76442</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -1382,7 +1752,7 @@
         <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
         <v>33</v>
@@ -1391,7 +1761,7 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>12679</v>
+        <v>20469</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -1402,7 +1772,7 @@
         <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
         <v>34</v>
@@ -1411,7 +1781,7 @@
         <v>32</v>
       </c>
       <c r="E4">
-        <v>27247</v>
+        <v>12680</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -1422,7 +1792,7 @@
         <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
         <v>35</v>
@@ -1431,7 +1801,7 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>28837</v>
+        <v>27166</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -1442,7 +1812,7 @@
         <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
         <v>36</v>
@@ -1451,7 +1821,7 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>17526</v>
+        <v>28931</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -1462,7 +1832,7 @@
         <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
         <v>37</v>
@@ -1471,7 +1841,7 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>25473</v>
+        <v>17522</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -1482,7 +1852,7 @@
         <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
         <v>38</v>
@@ -1491,7 +1861,7 @@
         <v>32</v>
       </c>
       <c r="E8">
-        <v>26040</v>
+        <v>25460</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -1502,7 +1872,7 @@
         <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
         <v>39</v>
@@ -1511,7 +1881,7 @@
         <v>32</v>
       </c>
       <c r="E9">
-        <v>29163</v>
+        <v>26038</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -1522,7 +1892,7 @@
         <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
         <v>40</v>
@@ -1531,7 +1901,7 @@
         <v>32</v>
       </c>
       <c r="E10">
-        <v>14533</v>
+        <v>29031</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -1542,22 +1912,19 @@
         <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="E11">
-        <v>75908</v>
+        <v>13714</v>
       </c>
       <c r="F11" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>33.40727048675293</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1565,22 +1932,19 @@
         <v>29</v>
       </c>
       <c r="B12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" t="s">
         <v>42</v>
       </c>
-      <c r="C12" t="s">
-        <v>33</v>
-      </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="E12">
-        <v>41486</v>
+        <v>9839</v>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>39.10600833286202</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1588,22 +1952,22 @@
         <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E13">
-        <v>55080</v>
+        <v>30367</v>
       </c>
       <c r="F13" t="b">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>36.41580662862886</v>
+        <v>18.66888805552653</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1611,22 +1975,22 @@
         <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E14">
-        <v>38480</v>
+        <v>50011</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>52.54031322109805</v>
+        <v>29.8489379099596</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1634,22 +1998,22 @@
         <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E15">
-        <v>54089</v>
+        <v>22728</v>
       </c>
       <c r="F15" t="b">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>48.52641683787445</v>
+        <v>30.13843950564897</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1657,22 +2021,22 @@
         <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D16" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E16">
-        <v>109371</v>
+        <v>31209</v>
       </c>
       <c r="F16" t="b">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>43.95975851895916</v>
+        <v>29.82710999397896</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1680,22 +2044,22 @@
         <v>29</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E17">
-        <v>114594</v>
+        <v>20385</v>
       </c>
       <c r="F17" t="b">
         <v>0</v>
       </c>
       <c r="G17">
-        <v>47.66666528012912</v>
+        <v>45.2326536046331</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1703,22 +2067,22 @@
         <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D18" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E18">
-        <v>214517</v>
+        <v>30894</v>
       </c>
       <c r="F18" t="b">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>54.12039256250473</v>
+        <v>44.25440481306403</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1726,22 +2090,22 @@
         <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E19">
-        <v>148198</v>
+        <v>62112</v>
       </c>
       <c r="F19" t="b">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>62.45280156429101</v>
+        <v>41.60465131856576</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1749,22 +2113,22 @@
         <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E20">
-        <v>146819</v>
+        <v>56231</v>
       </c>
       <c r="F20" t="b">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>64.61535076137665</v>
+        <v>42.48337866424902</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1772,22 +2136,22 @@
         <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E21">
-        <v>62154</v>
+        <v>104853</v>
       </c>
       <c r="F21" t="b">
         <v>0</v>
       </c>
       <c r="G21">
-        <v>58.58831514054636</v>
+        <v>44.61696885624684</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1795,22 +2159,22 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E22">
-        <v>92536</v>
+        <v>64312</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
       </c>
       <c r="G22">
-        <v>61.17961296635439</v>
+        <v>56.92083019869894</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1818,22 +2182,22 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" t="s">
         <v>42</v>
       </c>
-      <c r="C23" t="s">
-        <v>35</v>
-      </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E23">
-        <v>32754</v>
+        <v>33510</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
       </c>
       <c r="G23">
-        <v>44.72207430467374</v>
+        <v>58.0571388970703</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1841,22 +2205,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E24">
-        <v>55956</v>
+        <v>128650</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>50.20141212779129</v>
+        <v>79.09086996883087</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1864,22 +2228,22 @@
         <v>29</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E25">
-        <v>137517</v>
+        <v>113121</v>
       </c>
       <c r="F25" t="b">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>55.27255042243105</v>
+        <v>67.51598059052087</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1887,22 +2251,22 @@
         <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E26">
-        <v>122072</v>
+        <v>50271</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
       </c>
       <c r="G26">
-        <v>50.77722362493604</v>
+        <v>66.6618044873495</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1910,22 +2274,22 @@
         <v>29</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E27">
-        <v>175789</v>
+        <v>69901</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
       </c>
       <c r="G27">
-        <v>44.34972374296743</v>
+        <v>66.80588342110042</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1933,22 +2297,22 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E28">
-        <v>84850</v>
+        <v>22710</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
       </c>
       <c r="G28">
-        <v>35.7570291956038</v>
+        <v>50.3916391150953</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1956,22 +2320,22 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D29" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E29">
-        <v>4493</v>
+        <v>37563</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
       </c>
       <c r="G29">
-        <v>1.977378751870434</v>
+        <v>53.80747743876235</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1979,22 +2343,22 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D30" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E30">
-        <v>2446</v>
+        <v>85353</v>
       </c>
       <c r="F30" t="b">
         <v>0</v>
       </c>
       <c r="G30">
-        <v>2.305676526591633</v>
+        <v>57.17223409314695</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2002,22 +2366,22 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D31" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E31">
-        <v>3637</v>
+        <v>72471</v>
       </c>
       <c r="F31" t="b">
         <v>0</v>
       </c>
       <c r="G31">
-        <v>2.40458040501676</v>
+        <v>54.7529465095195</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2025,22 +2389,22 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D32" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E32">
-        <v>2005</v>
+        <v>124192</v>
       </c>
       <c r="F32" t="b">
         <v>0</v>
       </c>
       <c r="G32">
-        <v>2.737612474228212</v>
+        <v>52.84608543575298</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2048,22 +2412,22 @@
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C33" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D33" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E33">
-        <v>1418</v>
+        <v>44766</v>
       </c>
       <c r="F33" t="b">
         <v>0</v>
       </c>
       <c r="G33">
-        <v>1.272171034334263</v>
+        <v>39.62118865336107</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2071,22 +2435,22 @@
         <v>29</v>
       </c>
       <c r="B34" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34" t="s">
         <v>42</v>
       </c>
-      <c r="C34" t="s">
-        <v>37</v>
-      </c>
       <c r="D34" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E34">
-        <v>1910</v>
+        <v>22584</v>
       </c>
       <c r="F34" t="b">
         <v>0</v>
       </c>
       <c r="G34">
-        <v>0.7676910586097959</v>
+        <v>39.12749701138274</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2094,22 +2458,22 @@
         <v>29</v>
       </c>
       <c r="B35" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C35" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D35" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E35">
-        <v>3741</v>
+        <v>3644</v>
       </c>
       <c r="F35" t="b">
         <v>0</v>
       </c>
       <c r="G35">
-        <v>1.55611109493484</v>
+        <v>2.240241975642594</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2117,22 +2481,22 @@
         <v>29</v>
       </c>
       <c r="B36" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C36" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D36" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E36">
-        <v>6064</v>
+        <v>4415</v>
       </c>
       <c r="F36" t="b">
         <v>0</v>
       </c>
       <c r="G36">
-        <v>1.52988369452784</v>
+        <v>2.635081499519538</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2140,22 +2504,206 @@
         <v>29</v>
       </c>
       <c r="B37" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" t="s">
+        <v>34</v>
+      </c>
+      <c r="D37" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37">
+        <v>2413</v>
+      </c>
+      <c r="F37" t="b">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>3.199756007001538</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" t="s">
+        <v>29</v>
+      </c>
+      <c r="B38" t="s">
+        <v>45</v>
+      </c>
+      <c r="C38" t="s">
+        <v>35</v>
+      </c>
+      <c r="D38" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38">
+        <v>3523</v>
+      </c>
+      <c r="F38" t="b">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>3.367006584920627</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" t="s">
+        <v>29</v>
+      </c>
+      <c r="B39" t="s">
+        <v>45</v>
+      </c>
+      <c r="C39" t="s">
+        <v>36</v>
+      </c>
+      <c r="D39" t="s">
+        <v>48</v>
+      </c>
+      <c r="E39">
+        <v>1972</v>
+      </c>
+      <c r="F39" t="b">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>4.375707280271596</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" t="s">
+        <v>29</v>
+      </c>
+      <c r="B40" t="s">
+        <v>45</v>
+      </c>
+      <c r="C40" t="s">
+        <v>37</v>
+      </c>
+      <c r="D40" t="s">
+        <v>48</v>
+      </c>
+      <c r="E40">
+        <v>1353</v>
+      </c>
+      <c r="F40" t="b">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>1.938117748173614</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" t="s">
+        <v>29</v>
+      </c>
+      <c r="B41" t="s">
+        <v>45</v>
+      </c>
+      <c r="C41" t="s">
+        <v>38</v>
+      </c>
+      <c r="D41" t="s">
+        <v>48</v>
+      </c>
+      <c r="E41">
+        <v>1826</v>
+      </c>
+      <c r="F41" t="b">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>1.223114588287305</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" t="s">
+        <v>29</v>
+      </c>
+      <c r="B42" t="s">
+        <v>45</v>
+      </c>
+      <c r="C42" t="s">
+        <v>39</v>
+      </c>
+      <c r="D42" t="s">
+        <v>48</v>
+      </c>
+      <c r="E42">
+        <v>3658</v>
+      </c>
+      <c r="F42" t="b">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>2.76367482623149</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" t="s">
+        <v>29</v>
+      </c>
+      <c r="B43" t="s">
+        <v>45</v>
+      </c>
+      <c r="C43" t="s">
+        <v>40</v>
+      </c>
+      <c r="D43" t="s">
+        <v>48</v>
+      </c>
+      <c r="E43">
+        <v>5962</v>
+      </c>
+      <c r="F43" t="b">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>2.536945708000187</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" t="s">
+        <v>29</v>
+      </c>
+      <c r="B44" t="s">
+        <v>45</v>
+      </c>
+      <c r="C44" t="s">
+        <v>41</v>
+      </c>
+      <c r="D44" t="s">
+        <v>48</v>
+      </c>
+      <c r="E44">
+        <v>3907</v>
+      </c>
+      <c r="F44" t="b">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>3.457981147939992</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" t="s">
+        <v>29</v>
+      </c>
+      <c r="B45" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" t="s">
         <v>42</v>
       </c>
-      <c r="C37" t="s">
-        <v>40</v>
-      </c>
-      <c r="D37" t="s">
-        <v>45</v>
-      </c>
-      <c r="E37">
-        <v>4248</v>
-      </c>
-      <c r="F37" t="b">
-        <v>0</v>
-      </c>
-      <c r="G37">
-        <v>1.790169240105185</v>
+      <c r="D45" t="s">
+        <v>48</v>
+      </c>
+      <c r="E45">
+        <v>1625</v>
+      </c>
+      <c r="F45" t="b">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>2.815364091546978</v>
       </c>
     </row>
   </sheetData>
@@ -2165,7 +2713,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1">
@@ -2196,7 +2744,7 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
         <v>31</v>
@@ -2205,7 +2753,7 @@
         <v>32</v>
       </c>
       <c r="E2">
-        <v>36145</v>
+        <v>88532</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -2216,7 +2764,7 @@
         <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C3" t="s">
         <v>33</v>
@@ -2225,7 +2773,7 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>27117</v>
+        <v>29944</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -2236,7 +2784,7 @@
         <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s">
         <v>34</v>
@@ -2245,7 +2793,7 @@
         <v>32</v>
       </c>
       <c r="E4">
-        <v>60740</v>
+        <v>20991</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -2256,7 +2804,7 @@
         <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s">
         <v>35</v>
@@ -2265,7 +2813,7 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>39384</v>
+        <v>49199</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -2276,7 +2824,7 @@
         <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s">
         <v>36</v>
@@ -2285,7 +2833,7 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>37527</v>
+        <v>34390</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -2296,7 +2844,7 @@
         <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C7" t="s">
         <v>37</v>
@@ -2305,7 +2853,7 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>48380</v>
+        <v>28381</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -2316,7 +2864,7 @@
         <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C8" t="s">
         <v>38</v>
@@ -2325,7 +2873,7 @@
         <v>32</v>
       </c>
       <c r="E8">
-        <v>65207</v>
+        <v>34045</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -2336,7 +2884,7 @@
         <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
         <v>39</v>
@@ -2345,7 +2893,7 @@
         <v>32</v>
       </c>
       <c r="E9">
-        <v>77369</v>
+        <v>38165</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -2356,7 +2904,7 @@
         <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C10" t="s">
         <v>40</v>
@@ -2365,7 +2913,7 @@
         <v>32</v>
       </c>
       <c r="E10">
-        <v>43779</v>
+        <v>44539</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -2376,22 +2924,19 @@
         <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E11">
-        <v>210857</v>
+        <v>24235</v>
       </c>
       <c r="F11" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>99.67383134717109</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2399,22 +2944,19 @@
         <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E12">
-        <v>91206</v>
+        <v>17263</v>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>99.51771997206704</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2422,22 +2964,22 @@
         <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E13">
-        <v>117322</v>
+        <v>150081</v>
       </c>
       <c r="F13" t="b">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>99.62805706521739</v>
+        <v>99.67457212876317</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2445,22 +2987,22 @@
         <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E14">
-        <v>62476</v>
+        <v>157725</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>99.65545843169782</v>
+        <v>99.78047978136544</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2468,22 +3010,22 @@
         <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E15">
-        <v>91281</v>
+        <v>66974</v>
       </c>
       <c r="F15" t="b">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>99.80210360586911</v>
+        <v>99.81073307402274</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2491,22 +3033,22 @@
         <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D16" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E16">
-        <v>225450</v>
+        <v>82459</v>
       </c>
       <c r="F16" t="b">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>99.80477309852982</v>
+        <v>99.82929782082324</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2514,22 +3056,22 @@
         <v>29</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E17">
-        <v>200698</v>
+        <v>39533</v>
       </c>
       <c r="F17" t="b">
         <v>0</v>
       </c>
       <c r="G17">
-        <v>99.73066984694891</v>
+        <v>99.81064431427994</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2537,22 +3079,22 @@
         <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D18" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E18">
-        <v>347195</v>
+        <v>58901</v>
       </c>
       <c r="F18" t="b">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>99.72168288507714</v>
+        <v>99.91518379671253</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2560,22 +3102,22 @@
         <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E19">
-        <v>207395</v>
+        <v>140543</v>
       </c>
       <c r="F19" t="b">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>99.68517183369381</v>
+        <v>99.8841556152545</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2583,22 +3125,22 @@
         <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E20">
-        <v>263</v>
+        <v>120021</v>
       </c>
       <c r="F20" t="b">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>0.124322254628995</v>
+        <v>99.82367569635625</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2606,22 +3148,22 @@
         <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D21" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E21">
-        <v>91</v>
+        <v>219124</v>
       </c>
       <c r="F21" t="b">
         <v>0</v>
       </c>
       <c r="G21">
-        <v>0.0992929469273743</v>
+        <v>99.82915639706786</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2629,22 +3171,22 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D22" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E22">
-        <v>101</v>
+        <v>102237</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
       </c>
       <c r="G22">
-        <v>0.08576766304347827</v>
+        <v>99.77845877576515</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2652,22 +3194,22 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C23" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D23" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E23">
-        <v>30</v>
+        <v>50195</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
       </c>
       <c r="G23">
-        <v>0.04785299559752441</v>
+        <v>99.80117307883486</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2675,22 +3217,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C24" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D24" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E24">
-        <v>16</v>
+        <v>328</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>0.01749360390107367</v>
+        <v>0.2178374321748544</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2698,22 +3240,22 @@
         <v>29</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C25" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D25" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E25">
-        <v>112</v>
+        <v>261</v>
       </c>
       <c r="F25" t="b">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>0.04958143529401348</v>
+        <v>0.1651146313072524</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2721,22 +3263,22 @@
         <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C26" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D26" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E26">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
       </c>
       <c r="G26">
-        <v>0.06161796859471277</v>
+        <v>0.1341261680153798</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2744,22 +3286,22 @@
         <v>29</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C27" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D27" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E27">
-        <v>247</v>
+        <v>101</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
       </c>
       <c r="G27">
-        <v>0.07094357831366827</v>
+        <v>0.1222760290556901</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2767,22 +3309,22 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C28" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D28" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E28">
-        <v>122</v>
+        <v>30</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
       </c>
       <c r="G28">
-        <v>0.05863975006008171</v>
+        <v>0.07574227428802262</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2790,22 +3332,22 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D29" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E29">
-        <v>383</v>
+        <v>16</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
       </c>
       <c r="G29">
-        <v>0.1810472377296771</v>
+        <v>0.02714118505199233</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2813,22 +3355,22 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C30" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D30" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E30">
-        <v>325</v>
+        <v>112</v>
       </c>
       <c r="F30" t="b">
         <v>0</v>
       </c>
       <c r="G30">
-        <v>0.3546176675977654</v>
+        <v>0.07959859565334812</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2836,22 +3378,22 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D31" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E31">
-        <v>301</v>
+        <v>124</v>
       </c>
       <c r="F31" t="b">
         <v>0</v>
       </c>
       <c r="G31">
-        <v>0.2556046195652174</v>
+        <v>0.1031330832633304</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2859,22 +3401,22 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D32" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E32">
-        <v>165</v>
+        <v>246</v>
       </c>
       <c r="F32" t="b">
         <v>0</v>
       </c>
       <c r="G32">
-        <v>0.2631914757863842</v>
+        <v>0.1120734035234785</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2882,22 +3424,22 @@
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C33" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D33" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E33">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="F33" t="b">
         <v>0</v>
       </c>
       <c r="G33">
-        <v>0.167282587304017</v>
+        <v>0.1268738288569644</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2905,22 +3447,22 @@
         <v>29</v>
       </c>
       <c r="B34" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D34" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E34">
-        <v>309</v>
+        <v>54</v>
       </c>
       <c r="F34" t="b">
         <v>0</v>
       </c>
       <c r="G34">
-        <v>0.1367916384450908</v>
+        <v>0.1073665374291679</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2928,22 +3470,22 @@
         <v>29</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C35" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D35" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E35">
-        <v>372</v>
+        <v>71</v>
       </c>
       <c r="F35" t="b">
         <v>0</v>
       </c>
       <c r="G35">
-        <v>0.1848539057841383</v>
+        <v>0.04715383440370324</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2951,22 +3493,22 @@
         <v>29</v>
       </c>
       <c r="B36" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C36" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D36" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E36">
-        <v>653</v>
+        <v>49</v>
       </c>
       <c r="F36" t="b">
         <v>0</v>
       </c>
       <c r="G36">
-        <v>0.1875552900357303</v>
+        <v>0.03099853231438838</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2974,22 +3516,22 @@
         <v>29</v>
       </c>
       <c r="B37" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C37" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D37" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E37">
-        <v>472</v>
+        <v>24</v>
       </c>
       <c r="F37" t="b">
         <v>0</v>
       </c>
       <c r="G37">
-        <v>0.2268685412160538</v>
+        <v>0.03576697813743462</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2997,22 +3539,22 @@
         <v>29</v>
       </c>
       <c r="B38" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C38" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D38" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E38">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="F38" t="b">
         <v>0</v>
       </c>
       <c r="G38">
-        <v>0.02079916047025011</v>
+        <v>0.01937046004842615</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -3020,13 +3562,13 @@
         <v>29</v>
       </c>
       <c r="B39" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C39" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D39" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E39">
         <v>26</v>
@@ -3035,7 +3577,7 @@
         <v>0</v>
       </c>
       <c r="G39">
-        <v>0.02836941340782123</v>
+        <v>0.06564330438295295</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -3043,22 +3585,22 @@
         <v>29</v>
       </c>
       <c r="B40" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C40" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D40" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E40">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F40" t="b">
         <v>0</v>
       </c>
       <c r="G40">
-        <v>0.03057065217391305</v>
+        <v>0.03901545351223898</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -3066,22 +3608,22 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C41" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D41" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E41">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="F41" t="b">
         <v>0</v>
       </c>
       <c r="G41">
-        <v>0.03349709691826708</v>
+        <v>0.02558526288857618</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3089,22 +3631,22 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C42" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D42" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E42">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="F42" t="b">
         <v>0</v>
       </c>
       <c r="G42">
-        <v>0.01312020292580525</v>
+        <v>0.04740794956459541</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3112,22 +3654,22 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C43" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D43" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E43">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="F43" t="b">
         <v>0</v>
       </c>
       <c r="G43">
-        <v>0.008853827731073837</v>
+        <v>0.03371313764527401</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3135,22 +3677,22 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C44" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D44" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E44">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="F44" t="b">
         <v>0</v>
       </c>
       <c r="G44">
-        <v>0.02285827867223216</v>
+        <v>0.0653888194878201</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3158,22 +3700,22 @@
         <v>29</v>
       </c>
       <c r="B45" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D45" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E45">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="F45" t="b">
         <v>0</v>
       </c>
       <c r="G45">
-        <v>0.01981824657345389</v>
+        <v>0.04175365344467641</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3181,22 +3723,252 @@
         <v>29</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C46" t="s">
+        <v>31</v>
+      </c>
+      <c r="D46" t="s">
+        <v>53</v>
+      </c>
+      <c r="E46">
+        <v>91</v>
+      </c>
+      <c r="F46" t="b">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0.06043660465826753</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" t="s">
+        <v>29</v>
+      </c>
+      <c r="B47" t="s">
+        <v>49</v>
+      </c>
+      <c r="C47" t="s">
+        <v>33</v>
+      </c>
+      <c r="D47" t="s">
+        <v>53</v>
+      </c>
+      <c r="E47">
+        <v>37</v>
+      </c>
+      <c r="F47" t="b">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0.02340705501290551</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" t="s">
+        <v>29</v>
+      </c>
+      <c r="B48" t="s">
+        <v>49</v>
+      </c>
+      <c r="C48" t="s">
+        <v>34</v>
+      </c>
+      <c r="D48" t="s">
+        <v>53</v>
+      </c>
+      <c r="E48">
+        <v>13</v>
+      </c>
+      <c r="F48" t="b">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0.01937377982444375</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" t="s">
+        <v>29</v>
+      </c>
+      <c r="B49" t="s">
+        <v>49</v>
+      </c>
+      <c r="C49" t="s">
+        <v>35</v>
+      </c>
+      <c r="D49" t="s">
+        <v>53</v>
+      </c>
+      <c r="E49">
+        <v>24</v>
+      </c>
+      <c r="F49" t="b">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>0.02905569007263923</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>29</v>
+      </c>
+      <c r="B50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C50" t="s">
+        <v>36</v>
+      </c>
+      <c r="D50" t="s">
+        <v>53</v>
+      </c>
+      <c r="E50">
+        <v>19</v>
+      </c>
+      <c r="F50" t="b">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>0.04797010704908099</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" t="s">
+        <v>29</v>
+      </c>
+      <c r="B51" t="s">
+        <v>49</v>
+      </c>
+      <c r="C51" t="s">
+        <v>37</v>
+      </c>
+      <c r="D51" t="s">
+        <v>53</v>
+      </c>
+      <c r="E51">
+        <v>11</v>
+      </c>
+      <c r="F51" t="b">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>0.01865956472324473</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" t="s">
+        <v>29</v>
+      </c>
+      <c r="B52" t="s">
+        <v>49</v>
+      </c>
+      <c r="C52" t="s">
+        <v>38</v>
+      </c>
+      <c r="D52" t="s">
+        <v>53</v>
+      </c>
+      <c r="E52">
+        <v>15</v>
+      </c>
+      <c r="F52" t="b">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>0.01066052620357341</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" t="s">
+        <v>29</v>
+      </c>
+      <c r="B53" t="s">
+        <v>49</v>
+      </c>
+      <c r="C53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D53" t="s">
+        <v>53</v>
+      </c>
+      <c r="E53">
+        <v>31</v>
+      </c>
+      <c r="F53" t="b">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>0.02578327081583259</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" t="s">
+        <v>29</v>
+      </c>
+      <c r="B54" t="s">
+        <v>49</v>
+      </c>
+      <c r="C54" t="s">
         <v>40</v>
       </c>
-      <c r="D46" t="s">
-        <v>50</v>
-      </c>
-      <c r="E46">
-        <v>61</v>
-      </c>
-      <c r="F46" t="b">
-        <v>0</v>
-      </c>
-      <c r="G46">
-        <v>0.02931987503004085</v>
+      <c r="D54" t="s">
+        <v>53</v>
+      </c>
+      <c r="E54">
+        <v>55</v>
+      </c>
+      <c r="F54" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0.02505706176337933</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" t="s">
+        <v>29</v>
+      </c>
+      <c r="B55" t="s">
+        <v>49</v>
+      </c>
+      <c r="C55" t="s">
+        <v>41</v>
+      </c>
+      <c r="D55" t="s">
+        <v>53</v>
+      </c>
+      <c r="E55">
+        <v>30</v>
+      </c>
+      <c r="F55" t="b">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0.02927857589006871</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" t="s">
+        <v>29</v>
+      </c>
+      <c r="B56" t="s">
+        <v>49</v>
+      </c>
+      <c r="C56" t="s">
+        <v>42</v>
+      </c>
+      <c r="D56" t="s">
+        <v>53</v>
+      </c>
+      <c r="E56">
+        <v>25</v>
+      </c>
+      <c r="F56" t="b">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>0.04970673029128144</v>
       </c>
     </row>
   </sheetData>
@@ -3206,7 +3978,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1">
@@ -3234,19 +4006,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
         <v>32</v>
       </c>
       <c r="E2">
-        <v>6656</v>
+        <v>0</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -3254,19 +4026,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
         <v>32</v>
       </c>
       <c r="E3">
-        <v>1011</v>
+        <v>0</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -3274,19 +4046,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
         <v>32</v>
       </c>
       <c r="E4">
-        <v>732</v>
+        <v>0</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -3294,19 +4066,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
         <v>32</v>
       </c>
       <c r="E5">
-        <v>903</v>
+        <v>0</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -3314,19 +4086,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
         <v>32</v>
       </c>
       <c r="E6">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -3334,19 +4106,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
         <v>32</v>
       </c>
       <c r="E7">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -3354,19 +4126,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
         <v>32</v>
       </c>
       <c r="E8">
-        <v>576</v>
+        <v>0</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -3374,19 +4146,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
         <v>32</v>
       </c>
       <c r="E9">
-        <v>503</v>
+        <v>149</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -3394,19 +4166,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
         <v>32</v>
       </c>
       <c r="E10">
-        <v>539</v>
+        <v>0</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -3414,19 +4186,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
         <v>32</v>
       </c>
       <c r="E11">
-        <v>487</v>
+        <v>4</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -3434,692 +4206,781 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="E12">
-        <v>141766</v>
+        <v>22</v>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>51.5872900352246</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
         <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E13">
-        <v>9578</v>
+        <v>141766</v>
       </c>
       <c r="F13" t="b">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>30.2402677359265</v>
+        <v>64.65480284220992</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
         <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E14">
-        <v>4399</v>
+        <v>9578</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>22.15897642554906</v>
+        <v>52.73067606254129</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
         <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E15">
-        <v>4307</v>
+        <v>4399</v>
       </c>
       <c r="F15" t="b">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>14.55215055579958</v>
+        <v>52.07149621212122</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
         <v>35</v>
       </c>
       <c r="D16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E16">
-        <v>3093</v>
+        <v>4307</v>
       </c>
       <c r="F16" t="b">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>15.14914042219719</v>
+        <v>41.73045247553532</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
         <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E17">
-        <v>4308</v>
+        <v>3093</v>
       </c>
       <c r="F17" t="b">
         <v>0</v>
       </c>
       <c r="G17">
-        <v>22.95151838039424</v>
+        <v>40.95061564941084</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C18" t="s">
         <v>37</v>
       </c>
       <c r="D18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E18">
-        <v>3524</v>
+        <v>4308</v>
       </c>
       <c r="F18" t="b">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>10.01620100616775</v>
+        <v>71.14781172584641</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
         <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E19">
-        <v>4043</v>
+        <v>3536</v>
       </c>
       <c r="F19" t="b">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>11.38777004760161</v>
+        <v>42.59214647072994</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C20" t="s">
         <v>39</v>
       </c>
       <c r="D20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E20">
-        <v>2073</v>
+        <v>4036</v>
       </c>
       <c r="F20" t="b">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>4.848895958083832</v>
+        <v>62.45744351593934</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C21" t="s">
         <v>40</v>
       </c>
       <c r="D21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E21">
-        <v>1847</v>
+        <v>2068</v>
       </c>
       <c r="F21" t="b">
         <v>0</v>
       </c>
       <c r="G21">
-        <v>7.349196243832563</v>
+        <v>40.43801329683222</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="D22" t="s">
         <v>55</v>
       </c>
       <c r="E22">
-        <v>62198</v>
+        <v>1875</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
       </c>
       <c r="G22">
-        <v>22.6332566737504</v>
+        <v>51.215514886643</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C23" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="D23" t="s">
         <v>55</v>
       </c>
       <c r="E23">
-        <v>14520</v>
+        <v>676</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
       </c>
       <c r="G23">
-        <v>45.8434628863701</v>
+        <v>31.91690273843248</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B24" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D24" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="E24">
-        <v>12136</v>
+        <v>70844</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>61.13237960910739</v>
+        <v>32.30961480576104</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B25" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D25" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="E25">
-        <v>20179</v>
+        <v>7575</v>
       </c>
       <c r="F25" t="b">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>68.1792073520965</v>
+        <v>41.70336930191588</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B26" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D26" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="E26">
-        <v>13314</v>
+        <v>3317</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
       </c>
       <c r="G26">
-        <v>65.21036391242592</v>
+        <v>39.26373106060606</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B27" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D27" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="E27">
-        <v>13035</v>
+        <v>5111</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
       </c>
       <c r="G27">
-        <v>69.4459243473628</v>
+        <v>49.52039531053192</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B28" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D28" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="E28">
-        <v>27469</v>
+        <v>4010</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
       </c>
       <c r="G28">
-        <v>78.07463831964301</v>
+        <v>53.09148682642658</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B29" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D29" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="E29">
-        <v>29390</v>
+        <v>1427</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
       </c>
       <c r="G29">
-        <v>82.78173675464046</v>
+        <v>23.56729975227085</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B30" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D30" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="E30">
-        <v>38170</v>
+        <v>4190</v>
       </c>
       <c r="F30" t="b">
         <v>0</v>
       </c>
       <c r="G30">
-        <v>89.28237275449101</v>
+        <v>50.46976632136835</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B31" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D31" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="E31">
-        <v>21855</v>
+        <v>2070</v>
       </c>
       <c r="F31" t="b">
         <v>0</v>
       </c>
       <c r="G31">
-        <v>86.96084672926946</v>
+        <v>32.03342618384401</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B32" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D32" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="E32">
-        <v>70844</v>
+        <v>2509</v>
       </c>
       <c r="F32" t="b">
         <v>0</v>
       </c>
       <c r="G32">
-        <v>25.77945329102501</v>
+        <v>49.06140007821666</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B33" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C33" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D33" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="E33">
-        <v>7575</v>
+        <v>1353</v>
       </c>
       <c r="F33" t="b">
         <v>0</v>
       </c>
       <c r="G33">
-        <v>23.9162693777034</v>
+        <v>36.95711554220158</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B34" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C34" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D34" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="E34">
-        <v>3317</v>
+        <v>688</v>
       </c>
       <c r="F34" t="b">
         <v>0</v>
       </c>
       <c r="G34">
-        <v>16.70864396534354</v>
+        <v>32.48347497639282</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B35" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C35" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D35" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E35">
-        <v>5111</v>
+        <v>6656</v>
       </c>
       <c r="F35" t="b">
         <v>0</v>
       </c>
       <c r="G35">
-        <v>17.26864209210393</v>
+        <v>3.035582352029042</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B36" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C36" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D36" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E36">
-        <v>4010</v>
+        <v>1011</v>
       </c>
       <c r="F36" t="b">
         <v>0</v>
       </c>
       <c r="G36">
-        <v>19.64049566537689</v>
+        <v>5.565954635542832</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B37" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C37" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D37" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E37">
-        <v>1427</v>
+        <v>732</v>
       </c>
       <c r="F37" t="b">
         <v>0</v>
       </c>
       <c r="G37">
-        <v>7.602557272242941</v>
+        <v>8.664772727272728</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B38" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D38" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E38">
-        <v>4190</v>
+        <v>903</v>
       </c>
       <c r="F38" t="b">
         <v>0</v>
       </c>
       <c r="G38">
-        <v>11.90916067418924</v>
+        <v>8.749152213932758</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B39" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C39" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D39" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E39">
-        <v>2070</v>
+        <v>450</v>
       </c>
       <c r="F39" t="b">
         <v>0</v>
       </c>
       <c r="G39">
-        <v>5.830493197757936</v>
+        <v>5.957897524162584</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B40" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D40" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E40">
-        <v>2509</v>
+        <v>320</v>
       </c>
       <c r="F40" t="b">
         <v>0</v>
       </c>
       <c r="G40">
-        <v>5.86873128742515</v>
+        <v>5.284888521882741</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B41" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C41" t="s">
+        <v>38</v>
+      </c>
+      <c r="D41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E41">
+        <v>576</v>
+      </c>
+      <c r="F41" t="b">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>6.938087207901711</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" t="s">
+        <v>54</v>
+      </c>
+      <c r="B42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C42" t="s">
+        <v>39</v>
+      </c>
+      <c r="D42" t="s">
+        <v>44</v>
+      </c>
+      <c r="E42">
+        <v>356</v>
+      </c>
+      <c r="F42" t="b">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>5.509130300216651</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C43" t="s">
         <v>40</v>
       </c>
-      <c r="D41" t="s">
-        <v>56</v>
-      </c>
-      <c r="E41">
-        <v>1430</v>
-      </c>
-      <c r="F41" t="b">
-        <v>0</v>
-      </c>
-      <c r="G41">
-        <v>5.689957026897979</v>
+      <c r="D43" t="s">
+        <v>44</v>
+      </c>
+      <c r="E43">
+        <v>537</v>
+      </c>
+      <c r="F43" t="b">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>10.50058662495112</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" t="s">
+        <v>54</v>
+      </c>
+      <c r="B44" t="s">
+        <v>30</v>
+      </c>
+      <c r="C44" t="s">
+        <v>41</v>
+      </c>
+      <c r="D44" t="s">
+        <v>44</v>
+      </c>
+      <c r="E44">
+        <v>433</v>
+      </c>
+      <c r="F44" t="b">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>11.82736957115542</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" t="s">
+        <v>54</v>
+      </c>
+      <c r="B45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D45" t="s">
+        <v>44</v>
+      </c>
+      <c r="E45">
+        <v>754</v>
+      </c>
+      <c r="F45" t="b">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>35.59962228517469</v>
       </c>
     </row>
   </sheetData>
@@ -4129,7 +4990,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1">
@@ -4157,19 +5018,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
         <v>32</v>
       </c>
       <c r="E2">
-        <v>77419</v>
+        <v>77074</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -4177,19 +5038,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
         <v>32</v>
       </c>
       <c r="E3">
-        <v>8627</v>
+        <v>8526</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -4197,19 +5058,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
         <v>32</v>
       </c>
       <c r="E4">
-        <v>4076</v>
+        <v>4025</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -4217,19 +5078,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
         <v>32</v>
       </c>
       <c r="E5">
-        <v>6075</v>
+        <v>5951</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -4237,19 +5098,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
         <v>32</v>
       </c>
       <c r="E6">
-        <v>4493</v>
+        <v>4422</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -4257,19 +5118,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
         <v>32</v>
       </c>
       <c r="E7">
-        <v>1793</v>
+        <v>1724</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -4277,19 +5138,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
         <v>32</v>
       </c>
       <c r="E8">
-        <v>5000</v>
+        <v>4739</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -4297,19 +5158,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
         <v>32</v>
       </c>
       <c r="E9">
-        <v>2943</v>
+        <v>2558</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -4317,19 +5178,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
         <v>32</v>
       </c>
       <c r="E10">
-        <v>3397</v>
+        <v>3025</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -4337,19 +5198,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
         <v>32</v>
       </c>
       <c r="E11">
-        <v>2003</v>
+        <v>1762</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -4357,462 +5218,528 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="E12">
-        <v>25325</v>
+        <v>1440</v>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>12.41147786027592</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
         <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E13">
-        <v>8186</v>
+        <v>9281</v>
       </c>
       <c r="F13" t="b">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>34.02751797813526</v>
+        <v>6.527090131652977</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
         <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E14">
-        <v>9231</v>
+        <v>1329</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>55.91834262175914</v>
+        <v>13.78916787715294</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
         <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E15">
-        <v>12320</v>
+        <v>1573</v>
       </c>
       <c r="F15" t="b">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>50.44012282497441</v>
+        <v>35.56409676690029</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
         <v>35</v>
       </c>
       <c r="D16" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E16">
-        <v>11886</v>
+        <v>1318</v>
       </c>
       <c r="F16" t="b">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>72.59069256137779</v>
+        <v>30.16018306636156</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
         <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E17">
-        <v>12424</v>
+        <v>2126</v>
       </c>
       <c r="F17" t="b">
         <v>0</v>
       </c>
       <c r="G17">
-        <v>71.82748453489044</v>
+        <v>67.90162887256469</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
         <v>37</v>
       </c>
       <c r="D18" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E18">
-        <v>22458</v>
+        <v>3689</v>
       </c>
       <c r="F18" t="b">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>73.01277674826881</v>
+        <v>85.17663357192335</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
         <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E19">
-        <v>19989</v>
+        <v>2342</v>
       </c>
       <c r="F19" t="b">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>60.45730877415843</v>
+        <v>65.73112545607634</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
         <v>39</v>
       </c>
       <c r="D20" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E20">
-        <v>29523</v>
+        <v>3311</v>
       </c>
       <c r="F20" t="b">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>74.00360956534817</v>
+        <v>81.69257340241796</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
         <v>40</v>
       </c>
       <c r="D21" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E21">
-        <v>19682</v>
+        <v>1651</v>
       </c>
       <c r="F21" t="b">
         <v>0</v>
       </c>
       <c r="G21">
-        <v>83.34180216802169</v>
+        <v>79.03303015797032</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="D22" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E22">
-        <v>178720</v>
+        <v>1531</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
       </c>
       <c r="G22">
-        <v>87.58852213972408</v>
+        <v>80.45191802417236</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="D23" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E23">
-        <v>15871</v>
+        <v>580</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
       </c>
       <c r="G23">
-        <v>65.97248202186475</v>
+        <v>82.85714285714286</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D24" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="E24">
-        <v>7277</v>
+        <v>132911</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>44.08165737824085</v>
+        <v>93.47290986834702</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B25" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D25" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="E25">
-        <v>12105</v>
+        <v>8309</v>
       </c>
       <c r="F25" t="b">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>49.55987717502559</v>
+        <v>86.21083212284705</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D26" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="E26">
-        <v>4488</v>
+        <v>2850</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
       </c>
       <c r="G26">
-        <v>27.4093074386222</v>
+        <v>64.43590323309969</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D27" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="E27">
-        <v>4873</v>
+        <v>3052</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
       </c>
       <c r="G27">
-        <v>28.17251546510956</v>
+        <v>69.83981693363845</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D28" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="E28">
-        <v>8301</v>
+        <v>1005</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
       </c>
       <c r="G28">
-        <v>26.9872232517312</v>
+        <v>32.09837112743533</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D29" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="E29">
-        <v>13074</v>
+        <v>642</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
       </c>
       <c r="G29">
-        <v>39.54269122584157</v>
+        <v>14.82336642807666</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D30" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="E30">
-        <v>10371</v>
+        <v>1221</v>
       </c>
       <c r="F30" t="b">
         <v>0</v>
       </c>
       <c r="G30">
-        <v>25.99639043465183</v>
+        <v>34.26887454392366</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" t="s">
+        <v>47</v>
+      </c>
+      <c r="E31">
+        <v>742</v>
+      </c>
+      <c r="F31" t="b">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>18.30742659758204</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" t="s">
         <v>40</v>
       </c>
-      <c r="D31" t="s">
-        <v>58</v>
-      </c>
-      <c r="E31">
-        <v>3934</v>
-      </c>
-      <c r="F31" t="b">
-        <v>0</v>
-      </c>
-      <c r="G31">
-        <v>16.65819783197832</v>
+      <c r="D32" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32">
+        <v>438</v>
+      </c>
+      <c r="F32" t="b">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>20.96696984202968</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" t="s">
+        <v>47</v>
+      </c>
+      <c r="E33">
+        <v>372</v>
+      </c>
+      <c r="F33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>19.54808197582764</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34" t="s">
+        <v>42</v>
+      </c>
+      <c r="D34" t="s">
+        <v>47</v>
+      </c>
+      <c r="E34">
+        <v>120</v>
+      </c>
+      <c r="F34" t="b">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>17.14285714285714</v>
       </c>
     </row>
   </sheetData>
@@ -4822,7 +5749,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1">
@@ -4850,19 +5777,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
         <v>32</v>
       </c>
       <c r="E2">
-        <v>95076</v>
+        <v>83302</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -4870,19 +5797,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
         <v>32</v>
       </c>
       <c r="E3">
-        <v>11025</v>
+        <v>9144</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -4890,19 +5817,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
         <v>32</v>
       </c>
       <c r="E4">
-        <v>6049</v>
+        <v>4279</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -4910,19 +5837,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
         <v>32</v>
       </c>
       <c r="E5">
-        <v>8520</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -4930,19 +5857,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
         <v>32</v>
       </c>
       <c r="E6">
-        <v>8637</v>
+        <v>4725</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -4950,19 +5877,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
         <v>32</v>
       </c>
       <c r="E7">
-        <v>3517</v>
+        <v>2108</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -4970,19 +5897,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
         <v>32</v>
       </c>
       <c r="E8">
-        <v>10087</v>
+        <v>5152</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -4990,19 +5917,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
         <v>32</v>
       </c>
       <c r="E9">
-        <v>13574</v>
+        <v>3137</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -5010,19 +5937,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
         <v>32</v>
       </c>
       <c r="E10">
-        <v>12253</v>
+        <v>3333</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -5030,19 +5957,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
         <v>32</v>
       </c>
       <c r="E11">
-        <v>5760</v>
+        <v>1996</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -5050,692 +5977,781 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E12">
-        <v>186214</v>
+        <v>1569</v>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>99.90664635062343</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s">
         <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E13">
-        <v>21536</v>
+        <v>135903</v>
       </c>
       <c r="F13" t="b">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>99.43210674546378</v>
+        <v>99.95513518284251</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
         <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E14">
-        <v>14417</v>
+        <v>9002</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>99.18816649466804</v>
+        <v>99.80044345898006</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s">
         <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E15">
-        <v>21849</v>
+        <v>4153</v>
       </c>
       <c r="F15" t="b">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>99.40400363967244</v>
+        <v>99.616214919645</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
         <v>35</v>
       </c>
       <c r="D16" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E16">
-        <v>12141</v>
+        <v>3847</v>
       </c>
       <c r="F16" t="b">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>99.27228127555192</v>
+        <v>99.71487817522032</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
         <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E17">
-        <v>15491</v>
+        <v>2808</v>
       </c>
       <c r="F17" t="b">
         <v>0</v>
       </c>
       <c r="G17">
-        <v>99.47344763372503</v>
+        <v>99.29278642149929</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B18" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
         <v>37</v>
       </c>
       <c r="D18" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E18">
-        <v>25544</v>
+        <v>3929</v>
       </c>
       <c r="F18" t="b">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>99.50140230601433</v>
+        <v>99.54395743602737</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
         <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E19">
-        <v>22255</v>
+        <v>3143</v>
       </c>
       <c r="F19" t="b">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>99.21094864479315</v>
+        <v>99.77777777777777</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C20" t="s">
         <v>39</v>
       </c>
       <c r="D20" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E20">
-        <v>30814</v>
+        <v>3461</v>
       </c>
       <c r="F20" t="b">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>99.27830401443391</v>
+        <v>99.62579159470351</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
         <v>40</v>
       </c>
       <c r="D21" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E21">
-        <v>19732</v>
+        <v>1775</v>
       </c>
       <c r="F21" t="b">
         <v>0</v>
       </c>
       <c r="G21">
-        <v>99.36049146482702</v>
+        <v>99.66311061201573</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="D22" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E22">
-        <v>43</v>
+        <v>1660</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
       </c>
       <c r="G22">
-        <v>0.02307015473099127</v>
+        <v>99.46075494307969</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B23" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C23" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="D23" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E23">
-        <v>12</v>
+        <v>567</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
       </c>
       <c r="G23">
-        <v>0.05540421995475322</v>
+        <v>99.29947460595446</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" t="s">
         <v>51</v>
       </c>
-      <c r="B24" t="s">
-        <v>59</v>
-      </c>
-      <c r="C24" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" t="s">
-        <v>48</v>
-      </c>
       <c r="E24">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>0.04815961472308222</v>
+        <v>0.03162601865199612</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" t="s">
         <v>51</v>
       </c>
-      <c r="B25" t="s">
-        <v>59</v>
-      </c>
-      <c r="C25" t="s">
-        <v>34</v>
-      </c>
-      <c r="D25" t="s">
-        <v>48</v>
-      </c>
       <c r="E25">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F25" t="b">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>0.02274795268425842</v>
+        <v>0.1108647450110865</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" t="s">
         <v>51</v>
       </c>
-      <c r="B26" t="s">
-        <v>59</v>
-      </c>
-      <c r="C26" t="s">
-        <v>35</v>
-      </c>
-      <c r="D26" t="s">
-        <v>48</v>
-      </c>
       <c r="E26">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
       </c>
       <c r="G26">
-        <v>0.07358953393295176</v>
+        <v>0.167905972655313</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27" t="s">
         <v>51</v>
       </c>
-      <c r="B27" t="s">
-        <v>59</v>
-      </c>
-      <c r="C27" t="s">
-        <v>36</v>
-      </c>
-      <c r="D27" t="s">
-        <v>48</v>
-      </c>
       <c r="E27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
       </c>
       <c r="G27">
-        <v>0.0321068516021319</v>
+        <v>0.1036806635562468</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28" t="s">
         <v>51</v>
       </c>
-      <c r="B28" t="s">
-        <v>59</v>
-      </c>
-      <c r="C28" t="s">
-        <v>37</v>
-      </c>
-      <c r="D28" t="s">
-        <v>48</v>
-      </c>
       <c r="E28">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
       </c>
       <c r="G28">
-        <v>0.00779058896852602</v>
+        <v>0.2828854314002829</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" t="s">
         <v>51</v>
       </c>
-      <c r="B29" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" t="s">
-        <v>38</v>
-      </c>
-      <c r="D29" t="s">
-        <v>48</v>
-      </c>
       <c r="E29">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
       </c>
       <c r="G29">
-        <v>0.004457917261055635</v>
+        <v>0.1266784899923993</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" t="s">
         <v>51</v>
       </c>
-      <c r="B30" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30" t="s">
-        <v>39</v>
-      </c>
-      <c r="D30" t="s">
-        <v>48</v>
-      </c>
       <c r="E30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F30" t="b">
         <v>0</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>0.06349206349206349</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
+        <v>54</v>
+      </c>
+      <c r="B31" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" t="s">
         <v>51</v>
       </c>
-      <c r="B31" t="s">
-        <v>59</v>
-      </c>
-      <c r="C31" t="s">
-        <v>40</v>
-      </c>
-      <c r="D31" t="s">
-        <v>48</v>
-      </c>
       <c r="E31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" t="b">
         <v>0</v>
       </c>
       <c r="G31">
-        <v>0.01007100055390503</v>
+        <v>0.02878526194588371</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32" t="s">
+        <v>40</v>
+      </c>
+      <c r="D32" t="s">
         <v>51</v>
       </c>
-      <c r="B32" t="s">
-        <v>59</v>
-      </c>
-      <c r="C32" t="s">
-        <v>53</v>
-      </c>
-      <c r="D32" t="s">
-        <v>60</v>
-      </c>
       <c r="E32">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="F32" t="b">
         <v>0</v>
       </c>
       <c r="G32">
-        <v>0.07028349464557805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" t="s">
         <v>51</v>
       </c>
-      <c r="B33" t="s">
-        <v>59</v>
-      </c>
-      <c r="C33" t="s">
-        <v>31</v>
-      </c>
-      <c r="D33" t="s">
-        <v>60</v>
-      </c>
       <c r="E33">
-        <v>111</v>
+        <v>1</v>
       </c>
       <c r="F33" t="b">
         <v>0</v>
       </c>
       <c r="G33">
-        <v>0.5124890345814673</v>
+        <v>0.05991611743559017</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" t="s">
+        <v>42</v>
+      </c>
+      <c r="D34" t="s">
         <v>51</v>
       </c>
-      <c r="B34" t="s">
-        <v>59</v>
-      </c>
-      <c r="C34" t="s">
-        <v>33</v>
-      </c>
-      <c r="D34" t="s">
-        <v>60</v>
-      </c>
       <c r="E34">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="F34" t="b">
         <v>0</v>
       </c>
       <c r="G34">
-        <v>0.7636738906088751</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B35" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C35" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D35" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E35">
-        <v>126</v>
+        <v>18</v>
       </c>
       <c r="F35" t="b">
         <v>0</v>
       </c>
       <c r="G35">
-        <v>0.5732484076433121</v>
+        <v>0.01323879850548675</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B36" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C36" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D36" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E36">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="F36" t="b">
         <v>0</v>
       </c>
       <c r="G36">
-        <v>0.6541291905151267</v>
+        <v>0.08869179600886917</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B37" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C37" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D37" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E37">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="F37" t="b">
         <v>0</v>
       </c>
       <c r="G37">
-        <v>0.4944455146728312</v>
+        <v>0.2158791076996882</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B38" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D38" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E38">
-        <v>126</v>
+        <v>7</v>
       </c>
       <c r="F38" t="b">
         <v>0</v>
       </c>
       <c r="G38">
-        <v>0.4908071050171393</v>
+        <v>0.1814411612234318</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B39" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C39" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D39" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E39">
-        <v>176</v>
+        <v>12</v>
       </c>
       <c r="F39" t="b">
         <v>0</v>
       </c>
       <c r="G39">
-        <v>0.7845934379457917</v>
+        <v>0.4243281471004243</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B40" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D40" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E40">
-        <v>224</v>
+        <v>13</v>
       </c>
       <c r="F40" t="b">
         <v>0</v>
       </c>
       <c r="G40">
-        <v>0.7216959855660803</v>
+        <v>0.3293640739802381</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B41" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C41" t="s">
+        <v>38</v>
+      </c>
+      <c r="D41" t="s">
+        <v>52</v>
+      </c>
+      <c r="E41">
+        <v>5</v>
+      </c>
+      <c r="F41" t="b">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>0.1587301587301587</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" t="s">
+        <v>54</v>
+      </c>
+      <c r="B42" t="s">
+        <v>49</v>
+      </c>
+      <c r="C42" t="s">
+        <v>39</v>
+      </c>
+      <c r="D42" t="s">
+        <v>52</v>
+      </c>
+      <c r="E42">
+        <v>12</v>
+      </c>
+      <c r="F42" t="b">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0.3454231433506045</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43" t="s">
+        <v>49</v>
+      </c>
+      <c r="C43" t="s">
         <v>40</v>
       </c>
-      <c r="D41" t="s">
-        <v>60</v>
-      </c>
-      <c r="E41">
-        <v>125</v>
-      </c>
-      <c r="F41" t="b">
-        <v>0</v>
-      </c>
-      <c r="G41">
-        <v>0.6294375346190645</v>
+      <c r="D43" t="s">
+        <v>52</v>
+      </c>
+      <c r="E43">
+        <v>6</v>
+      </c>
+      <c r="F43" t="b">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0.3368893879842785</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" t="s">
+        <v>54</v>
+      </c>
+      <c r="B44" t="s">
+        <v>49</v>
+      </c>
+      <c r="C44" t="s">
+        <v>41</v>
+      </c>
+      <c r="D44" t="s">
+        <v>52</v>
+      </c>
+      <c r="E44">
+        <v>8</v>
+      </c>
+      <c r="F44" t="b">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0.4793289394847214</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" t="s">
+        <v>54</v>
+      </c>
+      <c r="B45" t="s">
+        <v>49</v>
+      </c>
+      <c r="C45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D45" t="s">
+        <v>52</v>
+      </c>
+      <c r="E45">
+        <v>4</v>
+      </c>
+      <c r="F45" t="b">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0.7005253940455342</v>
       </c>
     </row>
   </sheetData>
@@ -5745,7 +6761,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1">
@@ -5773,19 +6789,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
         <v>32</v>
       </c>
       <c r="E2">
-        <v>43119</v>
+        <v>35420</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -5793,19 +6809,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
         <v>32</v>
       </c>
       <c r="E3">
-        <v>3033</v>
+        <v>2277</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -5813,19 +6829,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
         <v>32</v>
       </c>
       <c r="E4">
-        <v>1722</v>
+        <v>1144</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -5833,19 +6849,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
         <v>32</v>
       </c>
       <c r="E5">
-        <v>2005</v>
+        <v>1125</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -5853,19 +6869,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
         <v>32</v>
       </c>
       <c r="E6">
-        <v>3033</v>
+        <v>1002</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -5873,19 +6889,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
         <v>32</v>
       </c>
       <c r="E7">
-        <v>1129</v>
+        <v>438</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -5893,19 +6909,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
         <v>32</v>
       </c>
       <c r="E8">
-        <v>1787</v>
+        <v>622</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -5913,19 +6929,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
         <v>32</v>
       </c>
       <c r="E9">
-        <v>2041</v>
+        <v>439</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -5933,19 +6949,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
         <v>32</v>
       </c>
       <c r="E10">
-        <v>1928</v>
+        <v>382</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -5953,19 +6969,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
         <v>32</v>
       </c>
       <c r="E11">
-        <v>727</v>
+        <v>162</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -5973,1382 +6989,1540 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="E12">
-        <v>6566</v>
+        <v>79</v>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>2.754830183137889</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C13" t="s">
         <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E13">
-        <v>1679</v>
+        <v>4000</v>
       </c>
       <c r="F13" t="b">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>5.66254089238137</v>
+        <v>2.175734038271162</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s">
         <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E14">
-        <v>949</v>
+        <v>566</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>5.031279821864065</v>
+        <v>3.562661295398754</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
         <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E15">
-        <v>1407</v>
+        <v>242</v>
       </c>
       <c r="F15" t="b">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>4.937708369889454</v>
+        <v>3.313253012048193</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
         <v>35</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E16">
-        <v>573</v>
+        <v>325</v>
       </c>
       <c r="F16" t="b">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>3.212964001345744</v>
+        <v>3.534145280556764</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B17" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C17" t="s">
         <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E17">
-        <v>478</v>
+        <v>179</v>
       </c>
       <c r="F17" t="b">
         <v>0</v>
       </c>
       <c r="G17">
-        <v>2.56989247311828</v>
+        <v>2.732407266066249</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C18" t="s">
         <v>37</v>
       </c>
       <c r="D18" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E18">
-        <v>746</v>
+        <v>98</v>
       </c>
       <c r="F18" t="b">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>2.195086067382669</v>
+        <v>1.744703578422645</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C19" t="s">
         <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E19">
-        <v>544</v>
+        <v>141</v>
       </c>
       <c r="F19" t="b">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>1.601648756072428</v>
+        <v>1.8359375</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C20" t="s">
         <v>39</v>
       </c>
       <c r="D20" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E20">
-        <v>964</v>
+        <v>76</v>
       </c>
       <c r="F20" t="b">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>2.330585305708</v>
+        <v>1.231367465975373</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C21" t="s">
         <v>40</v>
       </c>
       <c r="D21" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E21">
-        <v>677</v>
+        <v>80</v>
       </c>
       <c r="F21" t="b">
         <v>0</v>
       </c>
       <c r="G21">
-        <v>2.719749317049654</v>
+        <v>1.69061707523246</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C22" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" t="s">
+        <v>57</v>
+      </c>
+      <c r="E22">
         <v>53</v>
       </c>
-      <c r="D22" t="s">
-        <v>63</v>
-      </c>
-      <c r="E22">
-        <v>9818</v>
-      </c>
       <c r="F22" t="b">
         <v>0</v>
       </c>
       <c r="G22">
-        <v>4.119238918374625</v>
+        <v>1.512988866685698</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B23" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C23" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="D23" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E23">
-        <v>2289</v>
+        <v>34</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
       </c>
       <c r="G23">
-        <v>7.719807089136959</v>
+        <v>1.649684619116934</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B24" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C24" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D24" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E24">
-        <v>1236</v>
+        <v>6402</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>6.552857597285549</v>
+        <v>3.482262328252994</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B25" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D25" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E25">
-        <v>2070</v>
+        <v>752</v>
       </c>
       <c r="F25" t="b">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>7.264432356553781</v>
+        <v>4.733429848303645</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B26" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D26" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E26">
-        <v>753</v>
+        <v>386</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
       </c>
       <c r="G26">
-        <v>4.222272064595716</v>
+        <v>5.284775465498357</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B27" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D27" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E27">
-        <v>605</v>
+        <v>557</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
       </c>
       <c r="G27">
-        <v>3.252688172043011</v>
+        <v>6.056981296215746</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D28" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E28">
-        <v>1070</v>
+        <v>232</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
       </c>
       <c r="G28">
-        <v>3.14844784463734</v>
+        <v>3.541444054342848</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B29" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D29" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E29">
-        <v>821</v>
+        <v>112</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
       </c>
       <c r="G29">
-        <v>2.417194170469601</v>
+        <v>1.993946946768738</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B30" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D30" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E30">
-        <v>1367</v>
+        <v>203</v>
       </c>
       <c r="F30" t="b">
         <v>0</v>
       </c>
       <c r="G30">
-        <v>3.304886009235307</v>
+        <v>2.643229166666667</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D31" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E31">
-        <v>947</v>
+        <v>104</v>
       </c>
       <c r="F31" t="b">
         <v>0</v>
       </c>
       <c r="G31">
-        <v>3.804435159890728</v>
+        <v>1.685029163966299</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B32" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C32" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D32" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E32">
-        <v>9203</v>
+        <v>137</v>
       </c>
       <c r="F32" t="b">
         <v>0</v>
       </c>
       <c r="G32">
-        <v>3.861209591138896</v>
+        <v>2.895181741335588</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B33" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C33" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D33" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E33">
-        <v>2142</v>
+        <v>80</v>
       </c>
       <c r="F33" t="b">
         <v>0</v>
       </c>
       <c r="G33">
-        <v>7.22403966139422</v>
+        <v>2.28375677990294</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B34" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C34" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D34" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E34">
-        <v>1165</v>
+        <v>49</v>
       </c>
       <c r="F34" t="b">
         <v>0</v>
       </c>
       <c r="G34">
-        <v>6.176439401972219</v>
+        <v>2.377486656962639</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B35" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C35" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D35" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E35">
-        <v>1988</v>
+        <v>5592</v>
       </c>
       <c r="F35" t="b">
         <v>0</v>
       </c>
       <c r="G35">
-        <v>6.976662572381119</v>
+        <v>3.041676185503084</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B36" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C36" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D36" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E36">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="F36" t="b">
         <v>0</v>
       </c>
       <c r="G36">
-        <v>3.695188964898508</v>
+        <v>4.17951784477875</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B37" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C37" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D37" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E37">
-        <v>701</v>
+        <v>370</v>
       </c>
       <c r="F37" t="b">
         <v>0</v>
       </c>
       <c r="G37">
-        <v>3.768817204301075</v>
+        <v>5.065717415115006</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B38" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D38" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E38">
-        <v>954</v>
+        <v>533</v>
       </c>
       <c r="F38" t="b">
         <v>0</v>
       </c>
       <c r="G38">
-        <v>2.807120788583199</v>
+        <v>5.795998260113093</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B39" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C39" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D39" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E39">
-        <v>799</v>
+        <v>175</v>
       </c>
       <c r="F39" t="b">
         <v>0</v>
       </c>
       <c r="G39">
-        <v>2.352421610481378</v>
+        <v>2.671347885818959</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B40" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D40" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E40">
-        <v>1345</v>
+        <v>123</v>
       </c>
       <c r="F40" t="b">
         <v>0</v>
       </c>
       <c r="G40">
-        <v>3.251698377777241</v>
+        <v>2.18978102189781</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B41" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C41" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D41" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E41">
-        <v>986</v>
+        <v>167</v>
       </c>
       <c r="F41" t="b">
         <v>0</v>
       </c>
       <c r="G41">
-        <v>3.961112003856661</v>
+        <v>2.174479166666667</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B42" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C42" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="D42" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E42">
-        <v>1143</v>
+        <v>102</v>
       </c>
       <c r="F42" t="b">
         <v>0</v>
       </c>
       <c r="G42">
-        <v>0.4795569447649416</v>
+        <v>1.652624756966948</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B43" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C43" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D43" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E43">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="F43" t="b">
         <v>0</v>
       </c>
       <c r="G43">
-        <v>0.5429833732420491</v>
+        <v>2.874049027895182</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B44" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C44" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D44" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E44">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="F44" t="b">
         <v>0</v>
       </c>
       <c r="G44">
-        <v>0.3658148658678825</v>
+        <v>2.28375677990294</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B45" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C45" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D45" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E45">
-        <v>120</v>
+        <v>23</v>
       </c>
       <c r="F45" t="b">
         <v>0</v>
       </c>
       <c r="G45">
-        <v>0.4211265134234076</v>
+        <v>1.115963124696749</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B46" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C46" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D46" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E46">
-        <v>50</v>
+        <v>779</v>
       </c>
       <c r="F46" t="b">
         <v>0</v>
       </c>
       <c r="G46">
-        <v>0.28036335090277</v>
+        <v>0.4237242039533087</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B47" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C47" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D47" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E47">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="F47" t="b">
         <v>0</v>
       </c>
       <c r="G47">
-        <v>0.2419354838709677</v>
+        <v>0.4532007301567319</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C48" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D48" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E48">
-        <v>99</v>
+        <v>28</v>
       </c>
       <c r="F48" t="b">
         <v>0</v>
       </c>
       <c r="G48">
-        <v>0.2913049874944829</v>
+        <v>0.3833515881708653</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C49" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D49" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E49">
-        <v>132</v>
+        <v>47</v>
       </c>
       <c r="F49" t="b">
         <v>0</v>
       </c>
       <c r="G49">
-        <v>0.3886353599293391</v>
+        <v>0.5110917790343628</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B50" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C50" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D50" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E50">
-        <v>98</v>
+        <v>21</v>
       </c>
       <c r="F50" t="b">
         <v>0</v>
       </c>
       <c r="G50">
-        <v>0.2369267219495685</v>
+        <v>0.3205617462982751</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C51" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D51" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E51">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="F51" t="b">
         <v>0</v>
       </c>
       <c r="G51">
-        <v>0.2008677486742728</v>
+        <v>0.2848495638241054</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B52" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C52" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="D52" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E52">
-        <v>82511</v>
+        <v>24</v>
       </c>
       <c r="F52" t="b">
         <v>0</v>
       </c>
       <c r="G52">
-        <v>34.61830539763788</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C53" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D53" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E53">
-        <v>9189</v>
+        <v>22</v>
       </c>
       <c r="F53" t="b">
         <v>0</v>
       </c>
       <c r="G53">
-        <v>30.99052308522478</v>
+        <v>0.356448476992871</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B54" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C54" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D54" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E54">
-        <v>5803</v>
+        <v>13</v>
       </c>
       <c r="F54" t="b">
         <v>0</v>
       </c>
       <c r="G54">
-        <v>30.76556038596119</v>
+        <v>0.2747252747252747</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C55" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D55" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E55">
-        <v>7940</v>
+        <v>3</v>
       </c>
       <c r="F55" t="b">
         <v>0</v>
       </c>
       <c r="G55">
-        <v>27.86453763818214</v>
+        <v>0.08564087924636027</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C56" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D56" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E56">
-        <v>5317</v>
+        <v>5</v>
       </c>
       <c r="F56" t="b">
         <v>0</v>
       </c>
       <c r="G56">
-        <v>29.81383873500056</v>
+        <v>0.242600679281902</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B57" t="s">
+        <v>56</v>
+      </c>
+      <c r="C57" t="s">
+        <v>31</v>
+      </c>
+      <c r="D57" t="s">
         <v>61</v>
       </c>
-      <c r="C57" t="s">
-        <v>36</v>
-      </c>
-      <c r="D57" t="s">
-        <v>66</v>
-      </c>
       <c r="E57">
-        <v>6688</v>
+        <v>64956</v>
       </c>
       <c r="F57" t="b">
         <v>0</v>
       </c>
       <c r="G57">
-        <v>35.95698924731182</v>
+        <v>35.3317450474854</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B58" t="s">
+        <v>56</v>
+      </c>
+      <c r="C58" t="s">
+        <v>33</v>
+      </c>
+      <c r="D58" t="s">
         <v>61</v>
       </c>
-      <c r="C58" t="s">
-        <v>37</v>
-      </c>
-      <c r="D58" t="s">
-        <v>66</v>
-      </c>
       <c r="E58">
-        <v>13086</v>
+        <v>5507</v>
       </c>
       <c r="F58" t="b">
         <v>0</v>
       </c>
       <c r="G58">
-        <v>38.50522289245255</v>
+        <v>34.66356140240448</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B59" t="s">
+        <v>56</v>
+      </c>
+      <c r="C59" t="s">
+        <v>34</v>
+      </c>
+      <c r="D59" t="s">
         <v>61</v>
       </c>
-      <c r="C59" t="s">
-        <v>38</v>
-      </c>
-      <c r="D59" t="s">
-        <v>66</v>
-      </c>
       <c r="E59">
-        <v>12883</v>
+        <v>2248</v>
       </c>
       <c r="F59" t="b">
         <v>0</v>
       </c>
       <c r="G59">
-        <v>37.93022228764905</v>
+        <v>30.7776560788609</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B60" t="s">
+        <v>56</v>
+      </c>
+      <c r="C60" t="s">
+        <v>35</v>
+      </c>
+      <c r="D60" t="s">
         <v>61</v>
       </c>
-      <c r="C60" t="s">
-        <v>39</v>
-      </c>
-      <c r="D60" t="s">
-        <v>66</v>
-      </c>
       <c r="E60">
-        <v>16300</v>
+        <v>2719</v>
       </c>
       <c r="F60" t="b">
         <v>0</v>
       </c>
       <c r="G60">
-        <v>39.40719967120373</v>
+        <v>29.56720313179643</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B61" t="s">
+        <v>56</v>
+      </c>
+      <c r="C61" t="s">
+        <v>36</v>
+      </c>
+      <c r="D61" t="s">
         <v>61</v>
       </c>
-      <c r="C61" t="s">
-        <v>40</v>
-      </c>
-      <c r="D61" t="s">
-        <v>66</v>
-      </c>
       <c r="E61">
-        <v>8788</v>
+        <v>2232</v>
       </c>
       <c r="F61" t="b">
         <v>0</v>
       </c>
       <c r="G61">
-        <v>35.3045155069902</v>
+        <v>34.07113417798809</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B62" t="s">
+        <v>56</v>
+      </c>
+      <c r="C62" t="s">
+        <v>37</v>
+      </c>
+      <c r="D62" t="s">
         <v>61</v>
       </c>
-      <c r="C62" t="s">
-        <v>53</v>
-      </c>
-      <c r="D62" t="s">
-        <v>67</v>
-      </c>
       <c r="E62">
-        <v>129104</v>
+        <v>2284</v>
       </c>
       <c r="F62" t="b">
         <v>0</v>
       </c>
       <c r="G62">
-        <v>54.16685896494577</v>
+        <v>40.66227523589104</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B63" t="s">
+        <v>56</v>
+      </c>
+      <c r="C63" t="s">
+        <v>38</v>
+      </c>
+      <c r="D63" t="s">
         <v>61</v>
       </c>
-      <c r="C63" t="s">
-        <v>31</v>
-      </c>
-      <c r="D63" t="s">
-        <v>67</v>
-      </c>
       <c r="E63">
-        <v>14191</v>
+        <v>2890</v>
       </c>
       <c r="F63" t="b">
         <v>0</v>
       </c>
       <c r="G63">
-        <v>47.86010589862062</v>
+        <v>37.63020833333333</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B64" t="s">
+        <v>56</v>
+      </c>
+      <c r="C64" t="s">
+        <v>39</v>
+      </c>
+      <c r="D64" t="s">
         <v>61</v>
       </c>
-      <c r="C64" t="s">
-        <v>33</v>
-      </c>
-      <c r="D64" t="s">
-        <v>67</v>
-      </c>
       <c r="E64">
-        <v>9640</v>
+        <v>2301</v>
       </c>
       <c r="F64" t="b">
         <v>0</v>
       </c>
       <c r="G64">
-        <v>51.10804792704909</v>
+        <v>37.28127025275437</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B65" t="s">
+        <v>56</v>
+      </c>
+      <c r="C65" t="s">
+        <v>40</v>
+      </c>
+      <c r="D65" t="s">
         <v>61</v>
       </c>
-      <c r="C65" t="s">
-        <v>34</v>
-      </c>
-      <c r="D65" t="s">
-        <v>67</v>
-      </c>
       <c r="E65">
-        <v>14970</v>
+        <v>1686</v>
       </c>
       <c r="F65" t="b">
         <v>0</v>
       </c>
       <c r="G65">
-        <v>52.5355325495701</v>
+        <v>35.62975486052409</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B66" t="s">
+        <v>56</v>
+      </c>
+      <c r="C66" t="s">
+        <v>41</v>
+      </c>
+      <c r="D66" t="s">
         <v>61</v>
       </c>
-      <c r="C66" t="s">
-        <v>35</v>
-      </c>
-      <c r="D66" t="s">
-        <v>67</v>
-      </c>
       <c r="E66">
-        <v>10482</v>
+        <v>1155</v>
       </c>
       <c r="F66" t="b">
         <v>0</v>
       </c>
       <c r="G66">
-        <v>58.77537288325671</v>
+        <v>32.97173850984871</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B67" t="s">
+        <v>56</v>
+      </c>
+      <c r="C67" t="s">
+        <v>42</v>
+      </c>
+      <c r="D67" t="s">
         <v>61</v>
       </c>
-      <c r="C67" t="s">
-        <v>36</v>
-      </c>
-      <c r="D67" t="s">
-        <v>67</v>
-      </c>
       <c r="E67">
-        <v>10083</v>
+        <v>695</v>
       </c>
       <c r="F67" t="b">
         <v>0</v>
       </c>
       <c r="G67">
-        <v>54.20967741935484</v>
+        <v>33.72149442018438</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B68" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C68" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D68" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E68">
-        <v>18030</v>
+        <v>102117</v>
       </c>
       <c r="F68" t="b">
         <v>0</v>
       </c>
       <c r="G68">
-        <v>53.05281741944976</v>
+        <v>55.54485819653405</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B69" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C69" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D69" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E69">
-        <v>18786</v>
+        <v>8326</v>
       </c>
       <c r="F69" t="b">
         <v>0</v>
       </c>
       <c r="G69">
-        <v>55.3098778153982</v>
+        <v>52.40762887895764</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B70" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C70" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D70" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E70">
-        <v>21289</v>
+        <v>4030</v>
       </c>
       <c r="F70" t="b">
         <v>0</v>
       </c>
       <c r="G70">
-        <v>51.46870391412615</v>
+        <v>55.17524644030668</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B71" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C71" t="s">
+        <v>35</v>
+      </c>
+      <c r="D71" t="s">
+        <v>62</v>
+      </c>
+      <c r="E71">
+        <v>5015</v>
+      </c>
+      <c r="F71" t="b">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>54.5345802522836</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" t="s">
+        <v>54</v>
+      </c>
+      <c r="B72" t="s">
+        <v>56</v>
+      </c>
+      <c r="C72" t="s">
+        <v>36</v>
+      </c>
+      <c r="D72" t="s">
+        <v>62</v>
+      </c>
+      <c r="E72">
+        <v>3712</v>
+      </c>
+      <c r="F72" t="b">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>56.66310486948557</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" t="s">
+        <v>54</v>
+      </c>
+      <c r="B73" t="s">
+        <v>56</v>
+      </c>
+      <c r="C73" t="s">
+        <v>37</v>
+      </c>
+      <c r="D73" t="s">
+        <v>62</v>
+      </c>
+      <c r="E73">
+        <v>2984</v>
+      </c>
+      <c r="F73" t="b">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>53.12444365319566</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" t="s">
+        <v>54</v>
+      </c>
+      <c r="B74" t="s">
+        <v>56</v>
+      </c>
+      <c r="C74" t="s">
+        <v>38</v>
+      </c>
+      <c r="D74" t="s">
+        <v>62</v>
+      </c>
+      <c r="E74">
+        <v>4255</v>
+      </c>
+      <c r="F74" t="b">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>55.40364583333334</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" t="s">
+        <v>54</v>
+      </c>
+      <c r="B75" t="s">
+        <v>56</v>
+      </c>
+      <c r="C75" t="s">
+        <v>39</v>
+      </c>
+      <c r="D75" t="s">
+        <v>62</v>
+      </c>
+      <c r="E75">
+        <v>3567</v>
+      </c>
+      <c r="F75" t="b">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>57.79325988334414</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" t="s">
+        <v>54</v>
+      </c>
+      <c r="B76" t="s">
+        <v>56</v>
+      </c>
+      <c r="C76" t="s">
         <v>40</v>
       </c>
-      <c r="D71" t="s">
-        <v>67</v>
-      </c>
-      <c r="E71">
-        <v>13444</v>
-      </c>
-      <c r="F71" t="b">
-        <v>0</v>
-      </c>
-      <c r="G71">
-        <v>54.00932026353848</v>
+      <c r="D76" t="s">
+        <v>62</v>
+      </c>
+      <c r="E76">
+        <v>2680</v>
+      </c>
+      <c r="F76" t="b">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>56.63567202028741</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" t="s">
+        <v>54</v>
+      </c>
+      <c r="B77" t="s">
+        <v>56</v>
+      </c>
+      <c r="C77" t="s">
+        <v>41</v>
+      </c>
+      <c r="D77" t="s">
+        <v>62</v>
+      </c>
+      <c r="E77">
+        <v>2132</v>
+      </c>
+      <c r="F77" t="b">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>60.86211818441336</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" t="s">
+        <v>54</v>
+      </c>
+      <c r="B78" t="s">
+        <v>56</v>
+      </c>
+      <c r="C78" t="s">
+        <v>42</v>
+      </c>
+      <c r="D78" t="s">
+        <v>62</v>
+      </c>
+      <c r="E78">
+        <v>1255</v>
+      </c>
+      <c r="F78" t="b">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>60.8927704997574</v>
       </c>
     </row>
   </sheetData>
